--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Mistral-7B-Instruct-v0.3/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Mistral-7B-Instruct-v0.3/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8333333333333334</v>
+        <v>0.8382352941176471</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7605633802816901</v>
+        <v>0.7816901408450704</v>
       </c>
       <c r="D2">
-        <v>0.3820224719101123</v>
+        <v>0.3522727272727273</v>
       </c>
       <c r="E2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
